--- a/Plantilla-TT-Consolidada.xlsx
+++ b/Plantilla-TT-Consolidada.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="80">
   <si>
     <t>ATTRAPI · TT — Vista Consolidada · Cuatro Subdirecciones</t>
   </si>
@@ -52,7 +52,7 @@
     <t>SA-001</t>
   </si>
   <si>
-    <t>M. Hernández</t>
+    <t>Amanda</t>
   </si>
   <si>
     <t>Transferencia primaria expediente 2024 obras inducidas</t>
@@ -91,9 +91,6 @@
     <t>SA-003</t>
   </si>
   <si>
-    <t>P. Martínez</t>
-  </si>
-  <si>
     <t>Solicitud de baja documental ejercicios 2018-2019</t>
   </si>
   <si>
@@ -112,7 +109,7 @@
     <t>SGOI-001</t>
   </si>
   <si>
-    <t>J. López</t>
+    <t>Fabiola</t>
   </si>
   <si>
     <t>Reubicación líneas CFE km 42+300 Tramo II Querétaro-Irapuato</t>
@@ -130,9 +127,6 @@
     <t>SGOI-002</t>
   </si>
   <si>
-    <t>R. Domínguez</t>
-  </si>
-  <si>
     <t>Liberación derecho de vía Salinas Victoria NL</t>
   </si>
   <si>
@@ -148,9 +142,6 @@
     <t>SGOI-006</t>
   </si>
   <si>
-    <t>A. Ortiz</t>
-  </si>
-  <si>
     <t>Reporte mensual obras inducidas abril 2026</t>
   </si>
   <si>
@@ -169,7 +160,7 @@
     <t>SPAC-001</t>
   </si>
   <si>
-    <t>R. Sánchez</t>
+    <t>Mario</t>
   </si>
   <si>
     <t>Formalización contrato segmento 15A1 Saltillo-N. Laredo</t>
@@ -187,9 +178,6 @@
     <t>SPAC-002</t>
   </si>
   <si>
-    <t>J. R. García</t>
-  </si>
-  <si>
     <t>Acto de fallo segmento 15A2 Saltillo-N. Laredo</t>
   </si>
   <si>
@@ -223,7 +211,7 @@
     <t>ENLACE-001</t>
   </si>
   <si>
-    <t>Lic. C. Méndez</t>
+    <t>Samanta</t>
   </si>
   <si>
     <t>Compilación de acuerdos del Comité Directivo abril 2026</t>
@@ -961,19 +949,19 @@
         <v>25</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="H6" s="8">
         <v>46203.25</v>
@@ -984,25 +972,25 @@
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="C7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="D7" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="F7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="G7" s="10" t="s">
         <v>36</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>37</v>
       </c>
       <c r="H7" s="11">
         <v>46203.25</v>
@@ -1013,25 +1001,25 @@
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="H8" s="8">
         <v>46172.25</v>
@@ -1042,25 +1030,25 @@
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="F9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="G9" s="10" t="s">
         <v>46</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="H9" s="11">
         <v>46149.25</v>
@@ -1071,25 +1059,25 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="E10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>56</v>
       </c>
       <c r="H10" s="8">
         <v>46152.25</v>
@@ -1100,25 +1088,25 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="G11" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="H11" s="11">
         <v>46129.25</v>
@@ -1129,25 +1117,25 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="H12" s="8">
         <v>46149.25</v>
@@ -1158,25 +1146,25 @@
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="F13" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="G13" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="H13" s="11">
         <v>46157.25</v>
@@ -1187,25 +1175,25 @@
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="H14" s="8">
         <v>46149.25</v>
@@ -1216,25 +1204,25 @@
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>72</v>
-      </c>
       <c r="F15" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H15" s="11">
         <v>46142.25</v>

--- a/Plantilla-TT-Consolidada.xlsx
+++ b/Plantilla-TT-Consolidada.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="83">
   <si>
     <t>ATTRAPI · TT — Vista Consolidada · Cuatro Subdirecciones</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Estatus</t>
   </si>
   <si>
+    <t>URL</t>
+  </si>
+  <si>
     <t>SA</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>En Proceso</t>
   </si>
   <si>
+    <t>https://drive.google.com/drive/folders/EJEMPLO</t>
+  </si>
+  <si>
     <t>SA-002</t>
   </si>
   <si>
@@ -86,6 +92,9 @@
   </si>
   <si>
     <t>Atendida</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>SA-003</t>
@@ -816,7 +825,7 @@
     <tabColor rgb="FF691C32"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" style="1" customWidth="1"/>
@@ -826,9 +835,10 @@
     <col min="6" max="7" width="38" style="1" customWidth="1"/>
     <col min="8" max="8" width="16" style="1" customWidth="1"/>
     <col min="9" max="9" width="14" style="1" customWidth="1"/>
+    <col min="10" max="10" width="32" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -840,8 +850,9 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -853,8 +864,9 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-    </row>
-    <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" ht="32" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -882,356 +894,395 @@
       <c r="I3" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4" s="8">
         <v>46157.25</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H5" s="11">
         <v>46147.25</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H6" s="8">
         <v>46203.25</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H7" s="11">
         <v>46203.25</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H8" s="8">
         <v>46172.25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H9" s="11">
         <v>46149.25</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H10" s="8">
         <v>46152.25</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H11" s="11">
         <v>46129.25</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H12" s="8">
         <v>46149.25</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H13" s="11">
         <v>46157.25</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H14" s="8">
         <v>46149.25</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H15" s="11">
         <v>46142.25</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1241,8 +1292,9 @@
       <c r="G16" s="7"/>
       <c r="H16" s="8"/>
       <c r="I16" s="9"/>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -1252,8 +1304,9 @@
       <c r="G17" s="10"/>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" s="10"/>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1263,8 +1316,9 @@
       <c r="G18" s="7"/>
       <c r="H18" s="8"/>
       <c r="I18" s="9"/>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" s="7"/>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -1274,8 +1328,9 @@
       <c r="G19" s="10"/>
       <c r="H19" s="11"/>
       <c r="I19" s="12"/>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1285,8 +1340,9 @@
       <c r="G20" s="7"/>
       <c r="H20" s="8"/>
       <c r="I20" s="9"/>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="7"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -1296,8 +1352,9 @@
       <c r="G21" s="10"/>
       <c r="H21" s="11"/>
       <c r="I21" s="12"/>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" s="10"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1307,8 +1364,9 @@
       <c r="G22" s="7"/>
       <c r="H22" s="8"/>
       <c r="I22" s="9"/>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22" s="7"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -1318,8 +1376,9 @@
       <c r="G23" s="10"/>
       <c r="H23" s="11"/>
       <c r="I23" s="12"/>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J23" s="10"/>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1329,8 +1388,9 @@
       <c r="G24" s="7"/>
       <c r="H24" s="8"/>
       <c r="I24" s="9"/>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J24" s="7"/>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
@@ -1340,8 +1400,9 @@
       <c r="G25" s="10"/>
       <c r="H25" s="11"/>
       <c r="I25" s="12"/>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J25" s="10"/>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1351,8 +1412,9 @@
       <c r="G26" s="7"/>
       <c r="H26" s="8"/>
       <c r="I26" s="9"/>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J26" s="7"/>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -1362,8 +1424,9 @@
       <c r="G27" s="10"/>
       <c r="H27" s="11"/>
       <c r="I27" s="12"/>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J27" s="10"/>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -1373,11 +1436,12 @@
       <c r="G28" s="7"/>
       <c r="H28" s="8"/>
       <c r="I28" s="9"/>
+      <c r="J28" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" sqref="A10:A28">

--- a/Plantilla-TT-Consolidada.xlsx
+++ b/Plantilla-TT-Consolidada.xlsx
@@ -55,7 +55,7 @@
     <t>SA-001</t>
   </si>
   <si>
-    <t>Amanda</t>
+    <t>AMANDA</t>
   </si>
   <si>
     <t>Transferencia primaria expediente 2024 obras inducidas</t>
@@ -118,7 +118,7 @@
     <t>SGOI-001</t>
   </si>
   <si>
-    <t>Fabiola</t>
+    <t>FABIOLA</t>
   </si>
   <si>
     <t>Reubicación líneas CFE km 42+300 Tramo II Querétaro-Irapuato</t>
@@ -169,7 +169,7 @@
     <t>SPAC-001</t>
   </si>
   <si>
-    <t>Mario</t>
+    <t>MARIO</t>
   </si>
   <si>
     <t>Formalización contrato segmento 15A1 Saltillo-N. Laredo</t>
@@ -220,7 +220,7 @@
     <t>ENLACE-001</t>
   </si>
   <si>
-    <t>Samanta</t>
+    <t>SAMANTA</t>
   </si>
   <si>
     <t>Compilación de acuerdos del Comité Directivo abril 2026</t>
